--- a/Population/BCIO_Population_Expanded.xlsx
+++ b/Population/BCIO_Population_Expanded.xlsx
@@ -6054,12 +6054,6 @@
           <t>material entity</t>
         </is>
       </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>'organization' or 'Homo sapiens'
-and 'bearer of' some 'owner role'</t>
-        </is>
-      </c>
       <c r="N142" t="inlineStr">
         <is>
           <t>percentage; proportion</t>
